--- a/labs/lab-03-create-and-refine-recruitment-charts-with-copilot/data/BrightPath_Recruitment_Metrics.xlsx
+++ b/labs/lab-03-create-and-refine-recruitment-charts-with-copilot/data/BrightPath_Recruitment_Metrics.xlsx
@@ -20,11 +20,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="mmm-yyyy"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="&quot;S$&quot;#,##0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="mmm-yyyy"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="&quot;S$&quot;#,##0"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -72,16 +71,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -710,7 +715,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="n">
+      <c r="A2" s="7" t="n">
         <v>45658</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -738,15 +743,15 @@
       <c r="H2" t="n">
         <v>7</v>
       </c>
-      <c r="I2" s="5" t="n">
+      <c r="I2" s="8" t="n">
         <v>34.5</v>
       </c>
-      <c r="J2" s="6" t="n">
+      <c r="J2" s="9" t="n">
         <v>1960</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="7" t="n">
         <v>45658</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -774,15 +779,15 @@
       <c r="H3" t="n">
         <v>8</v>
       </c>
-      <c r="I3" s="5" t="n">
+      <c r="I3" s="8" t="n">
         <v>38.1</v>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="J3" s="9" t="n">
         <v>970</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="7" t="n">
         <v>45658</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -810,15 +815,15 @@
       <c r="H4" t="n">
         <v>12</v>
       </c>
-      <c r="I4" s="5" t="n">
+      <c r="I4" s="8" t="n">
         <v>27.9</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="J4" s="9" t="n">
         <v>990</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="7" t="n">
         <v>45658</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -846,15 +851,15 @@
       <c r="H5" t="n">
         <v>10</v>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="I5" s="8" t="n">
         <v>40.6</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="J5" s="9" t="n">
         <v>2440</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="7" t="n">
         <v>45658</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -882,15 +887,15 @@
       <c r="H6" t="n">
         <v>8</v>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="I6" s="8" t="n">
         <v>26.5</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="J6" s="9" t="n">
         <v>940</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="7" t="n">
         <v>45658</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -918,15 +923,15 @@
       <c r="H7" t="n">
         <v>14</v>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="I7" s="8" t="n">
         <v>22.5</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="J7" s="9" t="n">
         <v>1260</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="7" t="n">
         <v>45689</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -954,15 +959,15 @@
       <c r="H8" t="n">
         <v>7</v>
       </c>
-      <c r="I8" s="5" t="n">
+      <c r="I8" s="8" t="n">
         <v>37.5</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="J8" s="9" t="n">
         <v>1950</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="7" t="n">
         <v>45689</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -990,15 +995,15 @@
       <c r="H9" t="n">
         <v>7</v>
       </c>
-      <c r="I9" s="5" t="n">
+      <c r="I9" s="8" t="n">
         <v>35</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="J9" s="9" t="n">
         <v>1200</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="7" t="n">
         <v>45689</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -1026,15 +1031,15 @@
       <c r="H10" t="n">
         <v>11</v>
       </c>
-      <c r="I10" s="5" t="n">
+      <c r="I10" s="8" t="n">
         <v>17.7</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="J10" s="9" t="n">
         <v>1070</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="7" t="n">
         <v>45689</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -1062,15 +1067,15 @@
       <c r="H11" t="n">
         <v>10</v>
       </c>
-      <c r="I11" s="5" t="n">
+      <c r="I11" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="J11" s="9" t="n">
         <v>2270</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="7" t="n">
         <v>45689</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -1098,15 +1103,15 @@
       <c r="H12" t="n">
         <v>8</v>
       </c>
-      <c r="I12" s="5" t="n">
+      <c r="I12" s="8" t="n">
         <v>24.8</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="J12" s="9" t="n">
         <v>1010</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="7" t="n">
         <v>45689</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -1134,15 +1139,15 @@
       <c r="H13" t="n">
         <v>13</v>
       </c>
-      <c r="I13" s="5" t="n">
+      <c r="I13" s="8" t="n">
         <v>26.1</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="J13" s="9" t="n">
         <v>1090</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="7" t="n">
         <v>45717</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -1170,15 +1175,15 @@
       <c r="H14" t="n">
         <v>7</v>
       </c>
-      <c r="I14" s="5" t="n">
+      <c r="I14" s="8" t="n">
         <v>33.9</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="J14" s="9" t="n">
         <v>2250</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="7" t="n">
         <v>45717</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -1206,15 +1211,15 @@
       <c r="H15" t="n">
         <v>13</v>
       </c>
-      <c r="I15" s="5" t="n">
+      <c r="I15" s="8" t="n">
         <v>33.4</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="J15" s="9" t="n">
         <v>1250</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
+      <c r="A16" s="7" t="n">
         <v>45717</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -1242,15 +1247,15 @@
       <c r="H16" t="n">
         <v>11</v>
       </c>
-      <c r="I16" s="5" t="n">
+      <c r="I16" s="8" t="n">
         <v>26.8</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="J16" s="9" t="n">
         <v>1050</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="7" t="n">
         <v>45717</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -1278,15 +1283,15 @@
       <c r="H17" t="n">
         <v>9</v>
       </c>
-      <c r="I17" s="5" t="n">
+      <c r="I17" s="8" t="n">
         <v>37</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="J17" s="9" t="n">
         <v>2480</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
+      <c r="A18" s="7" t="n">
         <v>45717</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -1314,15 +1319,15 @@
       <c r="H18" t="n">
         <v>8</v>
       </c>
-      <c r="I18" s="5" t="n">
+      <c r="I18" s="8" t="n">
         <v>23.9</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="J18" s="9" t="n">
         <v>900</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
+      <c r="A19" s="7" t="n">
         <v>45717</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -1350,15 +1355,15 @@
       <c r="H19" t="n">
         <v>10</v>
       </c>
-      <c r="I19" s="5" t="n">
+      <c r="I19" s="8" t="n">
         <v>23.7</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="J19" s="9" t="n">
         <v>1030</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n">
+      <c r="A20" s="7" t="n">
         <v>45748</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -1386,15 +1391,15 @@
       <c r="H20" t="n">
         <v>6</v>
       </c>
-      <c r="I20" s="5" t="n">
+      <c r="I20" s="8" t="n">
         <v>33.2</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="J20" s="9" t="n">
         <v>2160</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
+      <c r="A21" s="7" t="n">
         <v>45748</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -1422,15 +1427,15 @@
       <c r="H21" t="n">
         <v>11</v>
       </c>
-      <c r="I21" s="5" t="n">
+      <c r="I21" s="8" t="n">
         <v>30.8</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="J21" s="9" t="n">
         <v>1120</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n">
+      <c r="A22" s="7" t="n">
         <v>45748</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -1458,15 +1463,15 @@
       <c r="H22" t="n">
         <v>12</v>
       </c>
-      <c r="I22" s="5" t="n">
+      <c r="I22" s="8" t="n">
         <v>27.6</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="J22" s="9" t="n">
         <v>990</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n">
+      <c r="A23" s="7" t="n">
         <v>45748</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -1494,15 +1499,15 @@
       <c r="H23" t="n">
         <v>14</v>
       </c>
-      <c r="I23" s="5" t="n">
+      <c r="I23" s="8" t="n">
         <v>39</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="J23" s="9" t="n">
         <v>2420</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="n">
+      <c r="A24" s="7" t="n">
         <v>45748</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -1530,15 +1535,15 @@
       <c r="H24" t="n">
         <v>7</v>
       </c>
-      <c r="I24" s="5" t="n">
+      <c r="I24" s="8" t="n">
         <v>26.1</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="J24" s="9" t="n">
         <v>1080</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="n">
+      <c r="A25" s="7" t="n">
         <v>45748</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -1566,15 +1571,15 @@
       <c r="H25" t="n">
         <v>9</v>
       </c>
-      <c r="I25" s="5" t="n">
+      <c r="I25" s="8" t="n">
         <v>26.5</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="J25" s="9" t="n">
         <v>1060</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="n">
+      <c r="A26" s="7" t="n">
         <v>45778</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -1602,15 +1607,15 @@
       <c r="H26" t="n">
         <v>8</v>
       </c>
-      <c r="I26" s="5" t="n">
+      <c r="I26" s="8" t="n">
         <v>38.3</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="J26" s="9" t="n">
         <v>2000</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="n">
+      <c r="A27" s="7" t="n">
         <v>45778</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -1638,15 +1643,15 @@
       <c r="H27" t="n">
         <v>10</v>
       </c>
-      <c r="I27" s="5" t="n">
+      <c r="I27" s="8" t="n">
         <v>31.8</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="J27" s="9" t="n">
         <v>1230</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="n">
+      <c r="A28" s="7" t="n">
         <v>45778</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -1674,15 +1679,15 @@
       <c r="H28" t="n">
         <v>11</v>
       </c>
-      <c r="I28" s="5" t="n">
+      <c r="I28" s="8" t="n">
         <v>25.3</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="J28" s="9" t="n">
         <v>1080</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="n">
+      <c r="A29" s="7" t="n">
         <v>45778</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -1710,15 +1715,15 @@
       <c r="H29" t="n">
         <v>14</v>
       </c>
-      <c r="I29" s="5" t="n">
+      <c r="I29" s="8" t="n">
         <v>39.1</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="J29" s="9" t="n">
         <v>2330</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="n">
+      <c r="A30" s="7" t="n">
         <v>45778</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -1746,15 +1751,15 @@
       <c r="H30" t="n">
         <v>8</v>
       </c>
-      <c r="I30" s="5" t="n">
+      <c r="I30" s="8" t="n">
         <v>22.3</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="J30" s="9" t="n">
         <v>1250</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n">
+      <c r="A31" s="7" t="n">
         <v>45778</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -1782,15 +1787,15 @@
       <c r="H31" t="n">
         <v>13</v>
       </c>
-      <c r="I31" s="5" t="n">
+      <c r="I31" s="8" t="n">
         <v>22.9</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="J31" s="9" t="n">
         <v>1140</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="n">
+      <c r="A32" s="7" t="n">
         <v>45809</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -1818,15 +1823,15 @@
       <c r="H32" t="n">
         <v>6</v>
       </c>
-      <c r="I32" s="5" t="n">
+      <c r="I32" s="8" t="n">
         <v>37.6</v>
       </c>
-      <c r="J32" s="6" t="n">
+      <c r="J32" s="9" t="n">
         <v>2010</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="n">
+      <c r="A33" s="7" t="n">
         <v>45809</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -1854,15 +1859,15 @@
       <c r="H33" t="n">
         <v>8</v>
       </c>
-      <c r="I33" s="5" t="n">
+      <c r="I33" s="8" t="n">
         <v>29.4</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="J33" s="9" t="n">
         <v>950</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="n">
+      <c r="A34" s="7" t="n">
         <v>45809</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -1890,15 +1895,15 @@
       <c r="H34" t="n">
         <v>10</v>
       </c>
-      <c r="I34" s="5" t="n">
+      <c r="I34" s="8" t="n">
         <v>28.1</v>
       </c>
-      <c r="J34" s="6" t="n">
+      <c r="J34" s="9" t="n">
         <v>1120</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="n">
+      <c r="A35" s="7" t="n">
         <v>45809</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -1926,15 +1931,15 @@
       <c r="H35" t="n">
         <v>10</v>
       </c>
-      <c r="I35" s="5" t="n">
+      <c r="I35" s="8" t="n">
         <v>38.1</v>
       </c>
-      <c r="J35" s="6" t="n">
+      <c r="J35" s="9" t="n">
         <v>2300</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="n">
+      <c r="A36" s="7" t="n">
         <v>45809</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -1962,15 +1967,15 @@
       <c r="H36" t="n">
         <v>6</v>
       </c>
-      <c r="I36" s="5" t="n">
+      <c r="I36" s="8" t="n">
         <v>24.2</v>
       </c>
-      <c r="J36" s="6" t="n">
+      <c r="J36" s="9" t="n">
         <v>1160</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="n">
+      <c r="A37" s="7" t="n">
         <v>45809</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -1998,15 +2003,15 @@
       <c r="H37" t="n">
         <v>11</v>
       </c>
-      <c r="I37" s="5" t="n">
+      <c r="I37" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="J37" s="6" t="n">
+      <c r="J37" s="9" t="n">
         <v>880</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="n">
+      <c r="A38" s="7" t="n">
         <v>45839</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -2034,15 +2039,15 @@
       <c r="H38" t="n">
         <v>7</v>
       </c>
-      <c r="I38" s="5" t="n">
+      <c r="I38" s="8" t="n">
         <v>37.4</v>
       </c>
-      <c r="J38" s="6" t="n">
+      <c r="J38" s="9" t="n">
         <v>2010</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="n">
+      <c r="A39" s="7" t="n">
         <v>45839</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -2070,15 +2075,15 @@
       <c r="H39" t="n">
         <v>10</v>
       </c>
-      <c r="I39" s="5" t="n">
+      <c r="I39" s="8" t="n">
         <v>31.2</v>
       </c>
-      <c r="J39" s="6" t="n">
+      <c r="J39" s="9" t="n">
         <v>1220</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="n">
+      <c r="A40" s="7" t="n">
         <v>45839</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -2106,15 +2111,15 @@
       <c r="H40" t="n">
         <v>9</v>
       </c>
-      <c r="I40" s="5" t="n">
+      <c r="I40" s="8" t="n">
         <v>22.4</v>
       </c>
-      <c r="J40" s="6" t="n">
+      <c r="J40" s="9" t="n">
         <v>1160</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="n">
+      <c r="A41" s="7" t="n">
         <v>45839</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -2142,15 +2147,15 @@
       <c r="H41" t="n">
         <v>13</v>
       </c>
-      <c r="I41" s="5" t="n">
+      <c r="I41" s="8" t="n">
         <v>36.9</v>
       </c>
-      <c r="J41" s="6" t="n">
+      <c r="J41" s="9" t="n">
         <v>2350</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="n">
+      <c r="A42" s="7" t="n">
         <v>45839</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -2178,15 +2183,15 @@
       <c r="H42" t="n">
         <v>7</v>
       </c>
-      <c r="I42" s="5" t="n">
+      <c r="I42" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="J42" s="6" t="n">
+      <c r="J42" s="9" t="n">
         <v>1160</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="n">
+      <c r="A43" s="7" t="n">
         <v>45839</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -2214,15 +2219,15 @@
       <c r="H43" t="n">
         <v>13</v>
       </c>
-      <c r="I43" s="5" t="n">
+      <c r="I43" s="8" t="n">
         <v>24.6</v>
       </c>
-      <c r="J43" s="6" t="n">
+      <c r="J43" s="9" t="n">
         <v>1030</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="n">
+      <c r="A44" s="7" t="n">
         <v>45870</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -2250,15 +2255,15 @@
       <c r="H44" t="n">
         <v>5</v>
       </c>
-      <c r="I44" s="5" t="n">
+      <c r="I44" s="8" t="n">
         <v>28.5</v>
       </c>
-      <c r="J44" s="6" t="n">
+      <c r="J44" s="9" t="n">
         <v>2090</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="n">
+      <c r="A45" s="7" t="n">
         <v>45870</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -2286,15 +2291,15 @@
       <c r="H45" t="n">
         <v>11</v>
       </c>
-      <c r="I45" s="5" t="n">
+      <c r="I45" s="8" t="n">
         <v>31.2</v>
       </c>
-      <c r="J45" s="6" t="n">
+      <c r="J45" s="9" t="n">
         <v>890</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="n">
+      <c r="A46" s="7" t="n">
         <v>45870</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -2322,15 +2327,15 @@
       <c r="H46" t="n">
         <v>11</v>
       </c>
-      <c r="I46" s="5" t="n">
+      <c r="I46" s="8" t="n">
         <v>21.8</v>
       </c>
-      <c r="J46" s="6" t="n">
+      <c r="J46" s="9" t="n">
         <v>1090</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="n">
+      <c r="A47" s="7" t="n">
         <v>45870</v>
       </c>
       <c r="B47" t="inlineStr">
@@ -2358,15 +2363,15 @@
       <c r="H47" t="n">
         <v>14</v>
       </c>
-      <c r="I47" s="5" t="n">
+      <c r="I47" s="8" t="n">
         <v>36.6</v>
       </c>
-      <c r="J47" s="6" t="n">
+      <c r="J47" s="9" t="n">
         <v>2400</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="n">
+      <c r="A48" s="7" t="n">
         <v>45870</v>
       </c>
       <c r="B48" t="inlineStr">
@@ -2394,15 +2399,15 @@
       <c r="H48" t="n">
         <v>7</v>
       </c>
-      <c r="I48" s="5" t="n">
+      <c r="I48" s="8" t="n">
         <v>27.3</v>
       </c>
-      <c r="J48" s="6" t="n">
+      <c r="J48" s="9" t="n">
         <v>1230</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="n">
+      <c r="A49" s="7" t="n">
         <v>45870</v>
       </c>
       <c r="B49" t="inlineStr">
@@ -2430,15 +2435,15 @@
       <c r="H49" t="n">
         <v>8</v>
       </c>
-      <c r="I49" s="5" t="n">
+      <c r="I49" s="8" t="n">
         <v>22.6</v>
       </c>
-      <c r="J49" s="6" t="n">
+      <c r="J49" s="9" t="n">
         <v>1080</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="n">
+      <c r="A50" s="7" t="n">
         <v>45901</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -2466,15 +2471,15 @@
       <c r="H50" t="n">
         <v>9</v>
       </c>
-      <c r="I50" s="5" t="n">
+      <c r="I50" s="8" t="n">
         <v>34.7</v>
       </c>
-      <c r="J50" s="6" t="n">
+      <c r="J50" s="9" t="n">
         <v>2280</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="n">
+      <c r="A51" s="7" t="n">
         <v>45901</v>
       </c>
       <c r="B51" t="inlineStr">
@@ -2502,15 +2507,15 @@
       <c r="H51" t="n">
         <v>11</v>
       </c>
-      <c r="I51" s="5" t="n">
+      <c r="I51" s="8" t="n">
         <v>33.3</v>
       </c>
-      <c r="J51" s="6" t="n">
+      <c r="J51" s="9" t="n">
         <v>1170</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="n">
+      <c r="A52" s="7" t="n">
         <v>45901</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -2538,15 +2543,15 @@
       <c r="H52" t="n">
         <v>12</v>
       </c>
-      <c r="I52" s="5" t="n">
+      <c r="I52" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="J52" s="6" t="n">
+      <c r="J52" s="9" t="n">
         <v>1100</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="n">
+      <c r="A53" s="7" t="n">
         <v>45901</v>
       </c>
       <c r="B53" t="inlineStr">
@@ -2574,15 +2579,15 @@
       <c r="H53" t="n">
         <v>16</v>
       </c>
-      <c r="I53" s="5" t="n">
+      <c r="I53" s="8" t="n">
         <v>47.2</v>
       </c>
-      <c r="J53" s="6" t="n">
+      <c r="J53" s="9" t="n">
         <v>2630</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="n">
+      <c r="A54" s="7" t="n">
         <v>45901</v>
       </c>
       <c r="B54" t="inlineStr">
@@ -2610,15 +2615,15 @@
       <c r="H54" t="n">
         <v>7</v>
       </c>
-      <c r="I54" s="5" t="n">
+      <c r="I54" s="8" t="n">
         <v>21.6</v>
       </c>
-      <c r="J54" s="6" t="n">
+      <c r="J54" s="9" t="n">
         <v>930</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="n">
+      <c r="A55" s="7" t="n">
         <v>45901</v>
       </c>
       <c r="B55" t="inlineStr">
@@ -2646,15 +2651,15 @@
       <c r="H55" t="n">
         <v>12</v>
       </c>
-      <c r="I55" s="5" t="n">
+      <c r="I55" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="J55" s="6" t="n">
+      <c r="J55" s="9" t="n">
         <v>860</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="n">
+      <c r="A56" s="7" t="n">
         <v>45931</v>
       </c>
       <c r="B56" t="inlineStr">
@@ -2682,15 +2687,15 @@
       <c r="H56" t="n">
         <v>8</v>
       </c>
-      <c r="I56" s="5" t="n">
+      <c r="I56" s="8" t="n">
         <v>39.9</v>
       </c>
-      <c r="J56" s="6" t="n">
+      <c r="J56" s="9" t="n">
         <v>1950</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="n">
+      <c r="A57" s="7" t="n">
         <v>45931</v>
       </c>
       <c r="B57" t="inlineStr">
@@ -2718,15 +2723,15 @@
       <c r="H57" t="n">
         <v>11</v>
       </c>
-      <c r="I57" s="5" t="n">
+      <c r="I57" s="8" t="n">
         <v>29.7</v>
       </c>
-      <c r="J57" s="6" t="n">
+      <c r="J57" s="9" t="n">
         <v>1110</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="n">
+      <c r="A58" s="7" t="n">
         <v>45931</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -2754,15 +2759,15 @@
       <c r="H58" t="n">
         <v>10</v>
       </c>
-      <c r="I58" s="5" t="n">
+      <c r="I58" s="8" t="n">
         <v>29.8</v>
       </c>
-      <c r="J58" s="6" t="n">
+      <c r="J58" s="9" t="n">
         <v>1280</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="n">
+      <c r="A59" s="7" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="inlineStr">
@@ -2790,15 +2795,15 @@
       <c r="H59" t="n">
         <v>11</v>
       </c>
-      <c r="I59" s="5" t="n">
+      <c r="I59" s="8" t="n">
         <v>36.5</v>
       </c>
-      <c r="J59" s="6" t="n">
+      <c r="J59" s="9" t="n">
         <v>2350</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="n">
+      <c r="A60" s="7" t="n">
         <v>45931</v>
       </c>
       <c r="B60" t="inlineStr">
@@ -2826,15 +2831,15 @@
       <c r="H60" t="n">
         <v>7</v>
       </c>
-      <c r="I60" s="5" t="n">
+      <c r="I60" s="8" t="n">
         <v>27.4</v>
       </c>
-      <c r="J60" s="6" t="n">
+      <c r="J60" s="9" t="n">
         <v>1010</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="n">
+      <c r="A61" s="7" t="n">
         <v>45931</v>
       </c>
       <c r="B61" t="inlineStr">
@@ -2862,15 +2867,15 @@
       <c r="H61" t="n">
         <v>10</v>
       </c>
-      <c r="I61" s="5" t="n">
+      <c r="I61" s="8" t="n">
         <v>23.2</v>
       </c>
-      <c r="J61" s="6" t="n">
+      <c r="J61" s="9" t="n">
         <v>960</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="n">
+      <c r="A62" s="7" t="n">
         <v>45962</v>
       </c>
       <c r="B62" t="inlineStr">
@@ -2898,15 +2903,15 @@
       <c r="H62" t="n">
         <v>9</v>
       </c>
-      <c r="I62" s="5" t="n">
+      <c r="I62" s="8" t="n">
         <v>42.1</v>
       </c>
-      <c r="J62" s="6" t="n">
+      <c r="J62" s="9" t="n">
         <v>2250</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="n">
+      <c r="A63" s="7" t="n">
         <v>45962</v>
       </c>
       <c r="B63" t="inlineStr">
@@ -2934,15 +2939,15 @@
       <c r="H63" t="n">
         <v>12</v>
       </c>
-      <c r="I63" s="5" t="n">
+      <c r="I63" s="8" t="n">
         <v>33.7</v>
       </c>
-      <c r="J63" s="6" t="n">
+      <c r="J63" s="9" t="n">
         <v>860</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="n">
+      <c r="A64" s="7" t="n">
         <v>45962</v>
       </c>
       <c r="B64" t="inlineStr">
@@ -2970,15 +2975,15 @@
       <c r="H64" t="n">
         <v>12</v>
       </c>
-      <c r="I64" s="5" t="n">
+      <c r="I64" s="8" t="n">
         <v>29.6</v>
       </c>
-      <c r="J64" s="6" t="n">
+      <c r="J64" s="9" t="n">
         <v>1090</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="n">
+      <c r="A65" s="7" t="n">
         <v>45962</v>
       </c>
       <c r="B65" t="inlineStr">
@@ -3006,15 +3011,15 @@
       <c r="H65" t="n">
         <v>14</v>
       </c>
-      <c r="I65" s="5" t="n">
+      <c r="I65" s="8" t="n">
         <v>37.9</v>
       </c>
-      <c r="J65" s="6" t="n">
+      <c r="J65" s="9" t="n">
         <v>2350</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="n">
+      <c r="A66" s="7" t="n">
         <v>45962</v>
       </c>
       <c r="B66" t="inlineStr">
@@ -3042,15 +3047,15 @@
       <c r="H66" t="n">
         <v>9</v>
       </c>
-      <c r="I66" s="5" t="n">
+      <c r="I66" s="8" t="n">
         <v>17.5</v>
       </c>
-      <c r="J66" s="6" t="n">
+      <c r="J66" s="9" t="n">
         <v>1170</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="n">
+      <c r="A67" s="7" t="n">
         <v>45962</v>
       </c>
       <c r="B67" t="inlineStr">
@@ -3078,15 +3083,15 @@
       <c r="H67" t="n">
         <v>12</v>
       </c>
-      <c r="I67" s="5" t="n">
+      <c r="I67" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="J67" s="6" t="n">
+      <c r="J67" s="9" t="n">
         <v>1040</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="n">
+      <c r="A68" s="7" t="n">
         <v>45992</v>
       </c>
       <c r="B68" t="inlineStr">
@@ -3114,15 +3119,15 @@
       <c r="H68" t="n">
         <v>7</v>
       </c>
-      <c r="I68" s="5" t="n">
+      <c r="I68" s="8" t="n">
         <v>35</v>
       </c>
-      <c r="J68" s="6" t="n">
+      <c r="J68" s="9" t="n">
         <v>2240</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="n">
+      <c r="A69" s="7" t="n">
         <v>45992</v>
       </c>
       <c r="B69" t="inlineStr">
@@ -3150,15 +3155,15 @@
       <c r="H69" t="n">
         <v>8</v>
       </c>
-      <c r="I69" s="5" t="n">
+      <c r="I69" s="8" t="n">
         <v>36.2</v>
       </c>
-      <c r="J69" s="6" t="n">
+      <c r="J69" s="9" t="n">
         <v>940</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="n">
+      <c r="A70" s="7" t="n">
         <v>45992</v>
       </c>
       <c r="B70" t="inlineStr">
@@ -3186,15 +3191,15 @@
       <c r="H70" t="n">
         <v>8</v>
       </c>
-      <c r="I70" s="5" t="n">
+      <c r="I70" s="8" t="n">
         <v>22.3</v>
       </c>
-      <c r="J70" s="6" t="n">
+      <c r="J70" s="9" t="n">
         <v>1110</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="n">
+      <c r="A71" s="7" t="n">
         <v>45992</v>
       </c>
       <c r="B71" t="inlineStr">
@@ -3222,15 +3227,15 @@
       <c r="H71" t="n">
         <v>12</v>
       </c>
-      <c r="I71" s="5" t="n">
+      <c r="I71" s="8" t="n">
         <v>43</v>
       </c>
-      <c r="J71" s="6" t="n">
+      <c r="J71" s="9" t="n">
         <v>2410</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="n">
+      <c r="A72" s="7" t="n">
         <v>45992</v>
       </c>
       <c r="B72" t="inlineStr">
@@ -3258,15 +3263,15 @@
       <c r="H72" t="n">
         <v>7</v>
       </c>
-      <c r="I72" s="5" t="n">
+      <c r="I72" s="8" t="n">
         <v>24.3</v>
       </c>
-      <c r="J72" s="6" t="n">
+      <c r="J72" s="9" t="n">
         <v>1020</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="n">
+      <c r="A73" s="7" t="n">
         <v>45992</v>
       </c>
       <c r="B73" t="inlineStr">
@@ -3294,15 +3299,15 @@
       <c r="H73" t="n">
         <v>8</v>
       </c>
-      <c r="I73" s="5" t="n">
+      <c r="I73" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="J73" s="6" t="n">
+      <c r="J73" s="9" t="n">
         <v>1250</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="4" t="n">
+      <c r="A74" s="7" t="n">
         <v>46023</v>
       </c>
       <c r="B74" t="inlineStr">
@@ -3330,15 +3335,15 @@
       <c r="H74" t="n">
         <v>10</v>
       </c>
-      <c r="I74" s="5" t="n">
+      <c r="I74" s="8" t="n">
         <v>26.9</v>
       </c>
-      <c r="J74" s="6" t="n">
+      <c r="J74" s="9" t="n">
         <v>2150</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="n">
+      <c r="A75" s="7" t="n">
         <v>46023</v>
       </c>
       <c r="B75" t="inlineStr">
@@ -3366,15 +3371,15 @@
       <c r="H75" t="n">
         <v>12</v>
       </c>
-      <c r="I75" s="5" t="n">
+      <c r="I75" s="8" t="n">
         <v>37.1</v>
       </c>
-      <c r="J75" s="6" t="n">
+      <c r="J75" s="9" t="n">
         <v>1040</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="n">
+      <c r="A76" s="7" t="n">
         <v>46023</v>
       </c>
       <c r="B76" t="inlineStr">
@@ -3402,15 +3407,15 @@
       <c r="H76" t="n">
         <v>9</v>
       </c>
-      <c r="I76" s="5" t="n">
+      <c r="I76" s="8" t="n">
         <v>25.1</v>
       </c>
-      <c r="J76" s="6" t="n">
+      <c r="J76" s="9" t="n">
         <v>900</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="n">
+      <c r="A77" s="7" t="n">
         <v>46023</v>
       </c>
       <c r="B77" t="inlineStr">
@@ -3438,15 +3443,15 @@
       <c r="H77" t="n">
         <v>14</v>
       </c>
-      <c r="I77" s="5" t="n">
+      <c r="I77" s="8" t="n">
         <v>40.3</v>
       </c>
-      <c r="J77" s="6" t="n">
+      <c r="J77" s="9" t="n">
         <v>2540</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="n">
+      <c r="A78" s="7" t="n">
         <v>46023</v>
       </c>
       <c r="B78" t="inlineStr">
@@ -3474,15 +3479,15 @@
       <c r="H78" t="n">
         <v>8</v>
       </c>
-      <c r="I78" s="5" t="n">
+      <c r="I78" s="8" t="n">
         <v>28.9</v>
       </c>
-      <c r="J78" s="6" t="n">
+      <c r="J78" s="9" t="n">
         <v>1020</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="n">
+      <c r="A79" s="7" t="n">
         <v>46023</v>
       </c>
       <c r="B79" t="inlineStr">
@@ -3510,15 +3515,15 @@
       <c r="H79" t="n">
         <v>9</v>
       </c>
-      <c r="I79" s="5" t="n">
+      <c r="I79" s="8" t="n">
         <v>22.9</v>
       </c>
-      <c r="J79" s="6" t="n">
+      <c r="J79" s="9" t="n">
         <v>940</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="4" t="n">
+      <c r="A80" s="7" t="n">
         <v>46054</v>
       </c>
       <c r="B80" t="inlineStr">
@@ -3546,15 +3551,15 @@
       <c r="H80" t="n">
         <v>5</v>
       </c>
-      <c r="I80" s="5" t="n">
+      <c r="I80" s="8" t="n">
         <v>38.8</v>
       </c>
-      <c r="J80" s="6" t="n">
+      <c r="J80" s="9" t="n">
         <v>2250</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="n">
+      <c r="A81" s="7" t="n">
         <v>46054</v>
       </c>
       <c r="B81" t="inlineStr">
@@ -3582,15 +3587,15 @@
       <c r="H81" t="n">
         <v>12</v>
       </c>
-      <c r="I81" s="5" t="n">
+      <c r="I81" s="8" t="n">
         <v>25.5</v>
       </c>
-      <c r="J81" s="6" t="n">
+      <c r="J81" s="9" t="n">
         <v>1170</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="n">
+      <c r="A82" s="7" t="n">
         <v>46054</v>
       </c>
       <c r="B82" t="inlineStr">
@@ -3618,15 +3623,15 @@
       <c r="H82" t="n">
         <v>12</v>
       </c>
-      <c r="I82" s="5" t="n">
+      <c r="I82" s="8" t="n">
         <v>22.2</v>
       </c>
-      <c r="J82" s="6" t="n">
+      <c r="J82" s="9" t="n">
         <v>1120</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="4" t="n">
+      <c r="A83" s="7" t="n">
         <v>46054</v>
       </c>
       <c r="B83" t="inlineStr">
@@ -3654,15 +3659,15 @@
       <c r="H83" t="n">
         <v>13</v>
       </c>
-      <c r="I83" s="5" t="n">
+      <c r="I83" s="8" t="n">
         <v>42.1</v>
       </c>
-      <c r="J83" s="6" t="n">
+      <c r="J83" s="9" t="n">
         <v>2320</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="4" t="n">
+      <c r="A84" s="7" t="n">
         <v>46054</v>
       </c>
       <c r="B84" t="inlineStr">
@@ -3690,15 +3695,15 @@
       <c r="H84" t="n">
         <v>7</v>
       </c>
-      <c r="I84" s="5" t="n">
+      <c r="I84" s="8" t="n">
         <v>24.8</v>
       </c>
-      <c r="J84" s="6" t="n">
+      <c r="J84" s="9" t="n">
         <v>920</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="4" t="n">
+      <c r="A85" s="7" t="n">
         <v>46054</v>
       </c>
       <c r="B85" t="inlineStr">
@@ -3726,15 +3731,15 @@
       <c r="H85" t="n">
         <v>10</v>
       </c>
-      <c r="I85" s="5" t="n">
+      <c r="I85" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="J85" s="6" t="n">
+      <c r="J85" s="9" t="n">
         <v>1120</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="4" t="n">
+      <c r="A86" s="7" t="n">
         <v>46082</v>
       </c>
       <c r="B86" t="inlineStr">
@@ -3762,15 +3767,15 @@
       <c r="H86" t="n">
         <v>7</v>
       </c>
-      <c r="I86" s="5" t="n">
+      <c r="I86" s="8" t="n">
         <v>33.6</v>
       </c>
-      <c r="J86" s="6" t="n">
+      <c r="J86" s="9" t="n">
         <v>1850</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="n">
+      <c r="A87" s="7" t="n">
         <v>46082</v>
       </c>
       <c r="B87" t="inlineStr">
@@ -3798,15 +3803,15 @@
       <c r="H87" t="n">
         <v>13</v>
       </c>
-      <c r="I87" s="5" t="n">
+      <c r="I87" s="8" t="n">
         <v>34.5</v>
       </c>
-      <c r="J87" s="6" t="n">
+      <c r="J87" s="9" t="n">
         <v>1140</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="4" t="n">
+      <c r="A88" s="7" t="n">
         <v>46082</v>
       </c>
       <c r="B88" t="inlineStr">
@@ -3834,15 +3839,15 @@
       <c r="H88" t="n">
         <v>13</v>
       </c>
-      <c r="I88" s="5" t="n">
+      <c r="I88" s="8" t="n">
         <v>26.7</v>
       </c>
-      <c r="J88" s="6" t="n">
+      <c r="J88" s="9" t="n">
         <v>1170</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="4" t="n">
+      <c r="A89" s="7" t="n">
         <v>46082</v>
       </c>
       <c r="B89" t="inlineStr">
@@ -3870,15 +3875,15 @@
       <c r="H89" t="n">
         <v>13</v>
       </c>
-      <c r="I89" s="5" t="n">
+      <c r="I89" s="8" t="n">
         <v>40.2</v>
       </c>
-      <c r="J89" s="6" t="n">
+      <c r="J89" s="9" t="n">
         <v>2540</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="4" t="n">
+      <c r="A90" s="7" t="n">
         <v>46082</v>
       </c>
       <c r="B90" t="inlineStr">
@@ -3906,15 +3911,15 @@
       <c r="H90" t="n">
         <v>7</v>
       </c>
-      <c r="I90" s="5" t="n">
+      <c r="I90" s="8" t="n">
         <v>29.2</v>
       </c>
-      <c r="J90" s="6" t="n">
+      <c r="J90" s="9" t="n">
         <v>840</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="4" t="n">
+      <c r="A91" s="7" t="n">
         <v>46082</v>
       </c>
       <c r="B91" t="inlineStr">
@@ -3942,15 +3947,15 @@
       <c r="H91" t="n">
         <v>8</v>
       </c>
-      <c r="I91" s="5" t="n">
+      <c r="I91" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="J91" s="6" t="n">
+      <c r="J91" s="9" t="n">
         <v>1080</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="4" t="n">
+      <c r="A92" s="7" t="n">
         <v>46113</v>
       </c>
       <c r="B92" t="inlineStr">
@@ -3978,15 +3983,15 @@
       <c r="H92" t="n">
         <v>7</v>
       </c>
-      <c r="I92" s="5" t="n">
+      <c r="I92" s="8" t="n">
         <v>38</v>
       </c>
-      <c r="J92" s="6" t="n">
+      <c r="J92" s="9" t="n">
         <v>2030</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="4" t="n">
+      <c r="A93" s="7" t="n">
         <v>46113</v>
       </c>
       <c r="B93" t="inlineStr">
@@ -4014,15 +4019,15 @@
       <c r="H93" t="n">
         <v>15</v>
       </c>
-      <c r="I93" s="5" t="n">
+      <c r="I93" s="8" t="n">
         <v>37.8</v>
       </c>
-      <c r="J93" s="6" t="n">
+      <c r="J93" s="9" t="n">
         <v>910</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="4" t="n">
+      <c r="A94" s="7" t="n">
         <v>46113</v>
       </c>
       <c r="B94" t="inlineStr">
@@ -4050,15 +4055,15 @@
       <c r="H94" t="n">
         <v>12</v>
       </c>
-      <c r="I94" s="5" t="n">
+      <c r="I94" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="J94" s="6" t="n">
+      <c r="J94" s="9" t="n">
         <v>990</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="4" t="n">
+      <c r="A95" s="7" t="n">
         <v>46113</v>
       </c>
       <c r="B95" t="inlineStr">
@@ -4086,15 +4091,15 @@
       <c r="H95" t="n">
         <v>15</v>
       </c>
-      <c r="I95" s="5" t="n">
+      <c r="I95" s="8" t="n">
         <v>40.8</v>
       </c>
-      <c r="J95" s="6" t="n">
+      <c r="J95" s="9" t="n">
         <v>2470</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="4" t="n">
+      <c r="A96" s="7" t="n">
         <v>46113</v>
       </c>
       <c r="B96" t="inlineStr">
@@ -4122,15 +4127,15 @@
       <c r="H96" t="n">
         <v>7</v>
       </c>
-      <c r="I96" s="5" t="n">
+      <c r="I96" s="8" t="n">
         <v>21.9</v>
       </c>
-      <c r="J96" s="6" t="n">
+      <c r="J96" s="9" t="n">
         <v>1220</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="4" t="n">
+      <c r="A97" s="7" t="n">
         <v>46113</v>
       </c>
       <c r="B97" t="inlineStr">
@@ -4158,15 +4163,15 @@
       <c r="H97" t="n">
         <v>11</v>
       </c>
-      <c r="I97" s="5" t="n">
+      <c r="I97" s="8" t="n">
         <v>21.5</v>
       </c>
-      <c r="J97" s="6" t="n">
+      <c r="J97" s="9" t="n">
         <v>1070</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="4" t="n">
+      <c r="A98" s="7" t="n">
         <v>46143</v>
       </c>
       <c r="B98" t="inlineStr">
@@ -4194,15 +4199,15 @@
       <c r="H98" t="n">
         <v>4</v>
       </c>
-      <c r="I98" s="5" t="n">
+      <c r="I98" s="8" t="n">
         <v>35</v>
       </c>
-      <c r="J98" s="6" t="n">
+      <c r="J98" s="9" t="n">
         <v>2000</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="4" t="n">
+      <c r="A99" s="7" t="n">
         <v>46143</v>
       </c>
       <c r="B99" t="inlineStr">
@@ -4230,15 +4235,15 @@
       <c r="H99" t="n">
         <v>10</v>
       </c>
-      <c r="I99" s="5" t="n">
+      <c r="I99" s="8" t="n">
         <v>30.3</v>
       </c>
-      <c r="J99" s="6" t="n">
+      <c r="J99" s="9" t="n">
         <v>1020</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="4" t="n">
+      <c r="A100" s="7" t="n">
         <v>46143</v>
       </c>
       <c r="B100" t="inlineStr">
@@ -4266,15 +4271,15 @@
       <c r="H100" t="n">
         <v>9</v>
       </c>
-      <c r="I100" s="5" t="n">
+      <c r="I100" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="J100" s="6" t="n">
+      <c r="J100" s="9" t="n">
         <v>1150</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="4" t="n">
+      <c r="A101" s="7" t="n">
         <v>46143</v>
       </c>
       <c r="B101" t="inlineStr">
@@ -4302,15 +4307,15 @@
       <c r="H101" t="n">
         <v>13</v>
       </c>
-      <c r="I101" s="5" t="n">
+      <c r="I101" s="8" t="n">
         <v>33.9</v>
       </c>
-      <c r="J101" s="6" t="n">
+      <c r="J101" s="9" t="n">
         <v>2290</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="4" t="n">
+      <c r="A102" s="7" t="n">
         <v>46143</v>
       </c>
       <c r="B102" t="inlineStr">
@@ -4338,15 +4343,15 @@
       <c r="H102" t="n">
         <v>9</v>
       </c>
-      <c r="I102" s="5" t="n">
+      <c r="I102" s="8" t="n">
         <v>28.4</v>
       </c>
-      <c r="J102" s="6" t="n">
+      <c r="J102" s="9" t="n">
         <v>960</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="4" t="n">
+      <c r="A103" s="7" t="n">
         <v>46143</v>
       </c>
       <c r="B103" t="inlineStr">
@@ -4374,15 +4379,15 @@
       <c r="H103" t="n">
         <v>10</v>
       </c>
-      <c r="I103" s="5" t="n">
+      <c r="I103" s="8" t="n">
         <v>24.3</v>
       </c>
-      <c r="J103" s="6" t="n">
+      <c r="J103" s="9" t="n">
         <v>1080</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="4" t="n">
+      <c r="A104" s="7" t="n">
         <v>46174</v>
       </c>
       <c r="B104" t="inlineStr">
@@ -4410,15 +4415,15 @@
       <c r="H104" t="n">
         <v>6</v>
       </c>
-      <c r="I104" s="5" t="n">
+      <c r="I104" s="8" t="n">
         <v>39.1</v>
       </c>
-      <c r="J104" s="6" t="n">
+      <c r="J104" s="9" t="n">
         <v>1910</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="4" t="n">
+      <c r="A105" s="7" t="n">
         <v>46174</v>
       </c>
       <c r="B105" t="inlineStr">
@@ -4446,15 +4451,15 @@
       <c r="H105" t="n">
         <v>8</v>
       </c>
-      <c r="I105" s="5" t="n">
+      <c r="I105" s="8" t="n">
         <v>34.3</v>
       </c>
-      <c r="J105" s="6" t="n">
+      <c r="J105" s="9" t="n">
         <v>1050</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="4" t="n">
+      <c r="A106" s="7" t="n">
         <v>46174</v>
       </c>
       <c r="B106" t="inlineStr">
@@ -4482,15 +4487,15 @@
       <c r="H106" t="n">
         <v>9</v>
       </c>
-      <c r="I106" s="5" t="n">
+      <c r="I106" s="8" t="n">
         <v>24.4</v>
       </c>
-      <c r="J106" s="6" t="n">
+      <c r="J106" s="9" t="n">
         <v>1290</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="4" t="n">
+      <c r="A107" s="7" t="n">
         <v>46174</v>
       </c>
       <c r="B107" t="inlineStr">
@@ -4518,15 +4523,15 @@
       <c r="H107" t="n">
         <v>16</v>
       </c>
-      <c r="I107" s="5" t="n">
+      <c r="I107" s="8" t="n">
         <v>39.4</v>
       </c>
-      <c r="J107" s="6" t="n">
+      <c r="J107" s="9" t="n">
         <v>2440</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="4" t="n">
+      <c r="A108" s="7" t="n">
         <v>46174</v>
       </c>
       <c r="B108" t="inlineStr">
@@ -4554,15 +4559,15 @@
       <c r="H108" t="n">
         <v>9</v>
       </c>
-      <c r="I108" s="5" t="n">
+      <c r="I108" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="J108" s="6" t="n">
+      <c r="J108" s="9" t="n">
         <v>1130</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="4" t="n">
+      <c r="A109" s="7" t="n">
         <v>46174</v>
       </c>
       <c r="B109" t="inlineStr">
@@ -4590,10 +4595,10 @@
       <c r="H109" t="n">
         <v>9</v>
       </c>
-      <c r="I109" s="5" t="n">
+      <c r="I109" s="8" t="n">
         <v>27.3</v>
       </c>
-      <c r="J109" s="6" t="n">
+      <c r="J109" s="9" t="n">
         <v>1140</v>
       </c>
     </row>
@@ -4654,7 +4659,7 @@
       <c r="C2" t="n">
         <v>17</v>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="9" t="n">
         <v>14900</v>
       </c>
     </row>
@@ -4670,7 +4675,7 @@
       <c r="C3" t="n">
         <v>10</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="9" t="n">
         <v>6200</v>
       </c>
     </row>
@@ -4686,7 +4691,7 @@
       <c r="C4" t="n">
         <v>7</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="9" t="n">
         <v>1300</v>
       </c>
     </row>
@@ -4702,7 +4707,7 @@
       <c r="C5" t="n">
         <v>11</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="9" t="n">
         <v>8500</v>
       </c>
     </row>
@@ -4718,7 +4723,7 @@
       <c r="C6" t="n">
         <v>8</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="9" t="n">
         <v>1600</v>
       </c>
     </row>
@@ -4734,7 +4739,7 @@
       <c r="C7" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="9" t="n">
         <v>2400</v>
       </c>
     </row>
@@ -4750,7 +4755,7 @@
       <c r="C8" t="n">
         <v>11</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="9" t="n">
         <v>2200</v>
       </c>
     </row>
@@ -4781,12 +4786,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
@@ -4824,7 +4829,437 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>2 · A</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>In Charts!A1:A4, type these four questions:
+Q1 Trend: How have total hires moved month by month since Jan 2025?
+Q2 Comparison: Which sector produced the most hires in Jan-Jun 2026?
+Q3 Funnel: Where do candidates drop out between application and hire in 2026?
+Q4 Efficiency: Which sources convert best, and at what cost per hire?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>2 · B</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Create a PivotTable from tblMonthly on a new sheet named Pivot_Trend with Month_Label in rows and Sum of Hires as values. Then create a line chart of total hires by month from that PivotTable. Show data labels and gridlines. Title: "Monthly hires, Jan 2025 - Jun 2026".</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>2 · C</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>In an empty cell on Pivot_Trend, add this formula. Tell me whether it matches the PivotTable grand total, and which month had the most hires:
+=SUM(tblMonthly[Hires])</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>3 · D</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Create a PivotTable on a new sheet Pivot_Sector from tblMonthly with Sector in rows and Sum of Hires, filtered to months in 2026 only. Create a bar chart from it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>3 · E</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Sort the bars from highest to lowest and change the title to state the leading sector.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>3 · F</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>In an empty cell on Pivot_Sector, add this formula and tell me if it matches Technology's bar:
+=SUMIFS(tblMonthly[Hires],tblMonthly[Sector],"Technology",tblMonthly[Month],"&gt;="&amp;DATE(2026,1,1))</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>4 · G</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>On the Charts sheet, build a small table of 2026 totals for Applications, Screened, Interviews, Offers and Hires from tblMonthly using SUMIFS on Month &gt;= 1 Jan 2026. Then create a funnel chart from it with data labels. Add a column showing each stage as a % of Applications.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>4 · H</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Show the formula in each value cell of the funnel table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>5 · I</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>In tblSources add Hire_Rate = Hires / Applications (percentage, 1 decimal) and Cost_per_Hire = Sourcing_Spend / Hires (S$, no decimals). Create a combo chart: Hire_Rate as clustered columns sorted highest first, Cost_per_Hire as a line on a secondary axis. Label both axes with units.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>5 · J</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Which source has the highest Hire_Rate, and which has the lowest Cost_per_Hire? Give both values.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>6 · K</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Make every chart title state the finding in one sentence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>6 · L</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Use the same blue colour for all hires series and format numbers with thousands separators.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>6 · M</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Move all four charts to the Charts sheet in a 2 x 2 grid of equal size.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>6 · N</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Add alt text to each chart describing what it shows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>7 · O</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Chat</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Review the four charts on the Charts sheet. For each, tell me which question at the top of the sheet it answers, whether the chart type suits that question, and one improvement. Do not change anything.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>7 · P</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Prompt_Log already lists every prompt in this lab. For each one I ran, fill in What Copilot did and How I verified, and set Decision to Keep. I will tell you any row to change to Revise or Undo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Extra 1</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Create a PivotTable from tblMonthly with Month_Label in rows, Sector in columns and Sum of Hires as values.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Extra 2</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Create a line chart showing total hires by month. Show data labels and gridlines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Extra 3</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Create a bar chart of 2026 hires by Sector, sorted from highest to lowest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Extra 4</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Create a funnel chart of 2026 Applications, Screened, Interviews, Offers and Hires with data labels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>Extra 5</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Create a combo chart of Hire_Rate as columns and Cost_per_Hire as a line on a secondary axis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Extra 6</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Change the chart title to: Technology led hiring in H1 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Extra 7</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Sort the bars from highest to lowest and add data labels formatted with thousands separators.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>Extra 8</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>Add alt text to this chart that describes the trend it shows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Extra 9</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Is a line chart the right choice for this data? Suggest a better chart if not, and explain why.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
